--- a/Parts_List.xlsx
+++ b/Parts_List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ebf621722ec30091/Documents/GitHub/Electra/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="129" documentId="11_F25DC773A252ABDACC10488CD99C7BE45BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C00ECC3-2714-458F-BF21-02483A8C9DAF}"/>
+  <xr:revisionPtr revIDLastSave="139" documentId="11_F25DC773A252ABDACC10488CD99C7BE45BDE58EC" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AC1B4C2-8CA1-48AF-8562-F4AF8DBF92C5}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="3250" yWindow="610" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3250" yWindow="610" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -116,12 +116,6 @@
     <t>Comparator</t>
   </si>
   <si>
-    <t>ADCMP602BRMZ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.digikey.com/en/products/detail/analog-devices-inc/ADCMP602BRMZ/1246079?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=23488058847&amp;gbraid=0AAAAADrbLlhqdpS2BDk2B49DHfvzsMiow&amp;gclid=Cj0KCQjw--7UBhCpARIsAGJBptjz5LqE8OcHvmHiOhrq6usICtNAqAg8_U_6Ia_Mlen3fB-20NmInQkaAt-xEALw_wcB </t>
-  </si>
-  <si>
     <t>Voltage Ref</t>
   </si>
   <si>
@@ -134,19 +128,25 @@
     <t>Buffer</t>
   </si>
   <si>
-    <t>TS5A3166DCKR</t>
-  </si>
-  <si>
     <t>Analog Switch</t>
   </si>
   <si>
-    <t>https://www.digikey.com/en/products/detail/texas-instruments/TS5A3166DCKR/716905</t>
-  </si>
-  <si>
     <t>https://www.digikey.com/en/products/detail/texas-instruments/OPA365AIDBVT/1572587</t>
   </si>
   <si>
     <t>OPA365AIDBVT</t>
+  </si>
+  <si>
+    <t>TS12A4514DBVR</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/texas-instruments/TS12A4514DBVR/2021911?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20228387720&amp;gbraid=0AAAAADrbLlgHebmmBnJlnnypo12JpOBuC&amp;gclid=CjwKCAjwwfnUBhAtEiwAfQpAYh5NspWaO7HRQQk5TRUvidbOWOCUXIOuD1DUMzeqXltMwAeep3kMxxoCDQwQAvD_BwE</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/analog-devices-inc/ADCMP601BKSZ-REEL7/1246078?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=120565755&amp;gbraid=0AAAAADrbLli4CQ3JIRp0Kfaj9RLe-50CT&amp;gclid=CjwKCAjwwfnUBhAtEiwAfQpAYk0Qj_naERjlPtXKH9Bq5t_NgV-xe1YU_-rOH-FGWxXJvTazpnlTCBoCUpcQAvD_BwE</t>
+  </si>
+  <si>
+    <t>ADCMP601BKSZ</t>
   </si>
 </sst>
 </file>
@@ -793,10 +793,10 @@
         <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D10" s="13">
         <v>6.81</v>
@@ -811,13 +811,13 @@
     </row>
     <row r="11" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="17" t="s">
-        <v>29</v>
-      </c>
       <c r="C11" s="18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D11" s="19">
         <v>2.23</v>
@@ -832,13 +832,13 @@
     </row>
     <row r="12" spans="1:7" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="15" t="s">
         <v>30</v>
-      </c>
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>34</v>
       </c>
       <c r="D12" s="13">
         <v>3.07</v>
@@ -851,35 +851,33 @@
         <v>6.14</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
         <v>32</v>
-      </c>
-      <c r="B13" t="s">
-        <v>31</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>33</v>
       </c>
       <c r="D13" s="13">
-        <v>0.43</v>
+        <v>0.69</v>
       </c>
       <c r="E13" s="14">
         <v>2</v>
       </c>
       <c r="F13" s="13">
         <f t="shared" si="0"/>
-        <v>0.86</v>
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C5" r:id="rId1" xr:uid="{2A81A5B3-81F3-4F3C-938F-EAFB8C8BF841}"/>
     <hyperlink ref="C9" r:id="rId2" xr:uid="{8824E85B-D683-465C-9C95-D48EEB893A05}"/>
-    <hyperlink ref="C10" r:id="rId3" display="https://www.digikey.com/en/products/detail/analog-devices-inc/ADCMP602BRMZ/1246079?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=23488058847&amp;gbraid=0AAAAADrbLlhqdpS2BDk2B49DHfvzsMiow&amp;gclid=Cj0KCQjw--7UBhCpARIsAGJBptjz5LqE8OcHvmHiOhrq6usICtNAqAg8_U_6Ia_Mlen3fB-20NmInQkaAt-xEALw_wcB " xr:uid="{419DC065-559D-4329-9DB6-C20D9532C0D4}"/>
-    <hyperlink ref="C13" r:id="rId4" xr:uid="{64D12004-5515-471F-9433-E1054E593D36}"/>
-    <hyperlink ref="C11" r:id="rId5" xr:uid="{09B468F7-DDBC-4BE0-B31E-10153183CAB5}"/>
-    <hyperlink ref="C12" r:id="rId6" xr:uid="{89DE04A8-67A4-48FA-AA49-6EBC56E009E4}"/>
+    <hyperlink ref="C11" r:id="rId3" xr:uid="{09B468F7-DDBC-4BE0-B31E-10153183CAB5}"/>
+    <hyperlink ref="C12" r:id="rId4" xr:uid="{89DE04A8-67A4-48FA-AA49-6EBC56E009E4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
